--- a/monet/tests/TestData/calibrate/pwrmeasured_488nm.xlsx
+++ b/monet/tests/TestData/calibrate/pwrmeasured_488nm.xlsx
@@ -444,13 +444,13 @@
         <v>30</v>
       </c>
       <c r="B2" t="n">
-        <v>135.0368387547641</v>
+        <v>132.7199109940279</v>
       </c>
       <c r="C2" t="n">
-        <v>396.7980259070387</v>
+        <v>393.8125934795827</v>
       </c>
       <c r="D2" t="n">
-        <v>821.4226424746483</v>
+        <v>824.8050178988709</v>
       </c>
     </row>
     <row r="3">
@@ -458,13 +458,13 @@
         <v>35</v>
       </c>
       <c r="B3" t="n">
-        <v>100.9452388733599</v>
+        <v>97.72111173218141</v>
       </c>
       <c r="C3" t="n">
-        <v>375.5615403755626</v>
+        <v>375.5677106619204</v>
       </c>
       <c r="D3" t="n">
-        <v>931.1335458414236</v>
+        <v>929.5348000540448</v>
       </c>
     </row>
     <row r="4">
@@ -472,13 +472,13 @@
         <v>40</v>
       </c>
       <c r="B4" t="n">
-        <v>66.43054191638657</v>
+        <v>65.38816261402206</v>
       </c>
       <c r="C4" t="n">
-        <v>328.2295902817706</v>
+        <v>326.1432572398589</v>
       </c>
       <c r="D4" t="n">
-        <v>994.9289317583992</v>
+        <v>991.1009269114203</v>
       </c>
     </row>
     <row r="5">
@@ -486,13 +486,13 @@
         <v>45</v>
       </c>
       <c r="B5" t="n">
-        <v>38.02455383585905</v>
+        <v>34.51716087313276</v>
       </c>
       <c r="C5" t="n">
-        <v>270.6084567981266</v>
+        <v>267.4348543220206</v>
       </c>
       <c r="D5" t="n">
-        <v>990.8022363980497</v>
+        <v>994.2890635909083</v>
       </c>
     </row>
     <row r="6">
@@ -500,13 +500,13 @@
         <v>50</v>
       </c>
       <c r="B6" t="n">
-        <v>13.82245199968109</v>
+        <v>12.65013179790133</v>
       </c>
       <c r="C6" t="n">
-        <v>199.0344856161874</v>
+        <v>206.0091371617102</v>
       </c>
       <c r="D6" t="n">
-        <v>932.7452909087993</v>
+        <v>933.9850142311033</v>
       </c>
     </row>
     <row r="7">
@@ -514,13 +514,13 @@
         <v>55</v>
       </c>
       <c r="B7" t="n">
-        <v>-0.5316422515042194</v>
+        <v>1.653563046520059</v>
       </c>
       <c r="C7" t="n">
-        <v>129.3735268635505</v>
+        <v>130.1914409368007</v>
       </c>
       <c r="D7" t="n">
-        <v>817.1624012326336</v>
+        <v>818.5722417238519</v>
       </c>
     </row>
     <row r="8">
@@ -528,13 +528,13 @@
         <v>60</v>
       </c>
       <c r="B8" t="n">
-        <v>0.6913311388541044</v>
+        <v>1.571047556079149</v>
       </c>
       <c r="C8" t="n">
-        <v>79.66073809769851</v>
+        <v>71.95981028174673</v>
       </c>
       <c r="D8" t="n">
-        <v>670.2895186215939</v>
+        <v>666.4484822874402</v>
       </c>
     </row>
     <row r="9">
@@ -542,13 +542,13 @@
         <v>65</v>
       </c>
       <c r="B9" t="n">
-        <v>16.19590211006326</v>
+        <v>12.68962676869912</v>
       </c>
       <c r="C9" t="n">
-        <v>26.78522715566289</v>
+        <v>27.3700511004334</v>
       </c>
       <c r="D9" t="n">
-        <v>496.1034381648907</v>
+        <v>496.8935892142599</v>
       </c>
     </row>
     <row r="10">
@@ -556,13 +556,13 @@
         <v>70</v>
       </c>
       <c r="B10" t="n">
-        <v>34.35685647433166</v>
+        <v>35.17633028082958</v>
       </c>
       <c r="C10" t="n">
-        <v>-0.1480999440328103</v>
+        <v>-1.978345582316195</v>
       </c>
       <c r="D10" t="n">
-        <v>334.7379363750384</v>
+        <v>329.6315490428585</v>
       </c>
     </row>
     <row r="11">
@@ -570,13 +570,13 @@
         <v>75</v>
       </c>
       <c r="B11" t="n">
-        <v>66.98641071262827</v>
+        <v>67.88958038145212</v>
       </c>
       <c r="C11" t="n">
-        <v>6.051148917771419</v>
+        <v>2.138631240061756</v>
       </c>
       <c r="D11" t="n">
-        <v>177.4358418189257</v>
+        <v>179.2534735355453</v>
       </c>
     </row>
     <row r="12">
@@ -584,13 +584,13 @@
         <v>80</v>
       </c>
       <c r="B12" t="n">
-        <v>98.75035359715085</v>
+        <v>96.11407178035499</v>
       </c>
       <c r="C12" t="n">
-        <v>25.47438929610197</v>
+        <v>25.30267674317626</v>
       </c>
       <c r="D12" t="n">
-        <v>63.71617298314167</v>
+        <v>63.90095457502222</v>
       </c>
     </row>
     <row r="13">
@@ -598,13 +598,13 @@
         <v>85</v>
       </c>
       <c r="B13" t="n">
-        <v>133.6492992820709</v>
+        <v>135.5200135082353</v>
       </c>
       <c r="C13" t="n">
-        <v>70.35869712151909</v>
+        <v>73.74491377629687</v>
       </c>
       <c r="D13" t="n">
-        <v>8.923955555949243</v>
+        <v>11.61249384589292</v>
       </c>
     </row>
     <row r="14">
@@ -612,13 +612,13 @@
         <v>90</v>
       </c>
       <c r="B14" t="n">
-        <v>169.4302993714962</v>
+        <v>160.064596429522</v>
       </c>
       <c r="C14" t="n">
-        <v>133.9395066917342</v>
+        <v>127.6747548041641</v>
       </c>
       <c r="D14" t="n">
-        <v>4.457960975897075</v>
+        <v>6.973260614411233</v>
       </c>
     </row>
     <row r="15">
@@ -626,13 +626,13 @@
         <v>95</v>
       </c>
       <c r="B15" t="n">
-        <v>192.0482685077966</v>
+        <v>187.3104237557953</v>
       </c>
       <c r="C15" t="n">
-        <v>201.0432689258882</v>
+        <v>198.6068293655372</v>
       </c>
       <c r="D15" t="n">
-        <v>62.104125549255</v>
+        <v>70.35074733012576</v>
       </c>
     </row>
     <row r="16">
@@ -640,13 +640,13 @@
         <v>100</v>
       </c>
       <c r="B16" t="n">
-        <v>197.6406959580656</v>
+        <v>199.8802084100779</v>
       </c>
       <c r="C16" t="n">
-        <v>267.3240144310544</v>
+        <v>268.7238788299074</v>
       </c>
       <c r="D16" t="n">
-        <v>177.8859416522663</v>
+        <v>176.3457133697485</v>
       </c>
     </row>
   </sheetData>

--- a/monet/tests/TestData/calibrate/pwrmeasured_488nm.xlsx
+++ b/monet/tests/TestData/calibrate/pwrmeasured_488nm.xlsx
@@ -444,13 +444,13 @@
         <v>30</v>
       </c>
       <c r="B2" t="n">
-        <v>132.7199109940279</v>
+        <v>132.6974911867955</v>
       </c>
       <c r="C2" t="n">
-        <v>393.8125934795827</v>
+        <v>398.7140033108793</v>
       </c>
       <c r="D2" t="n">
-        <v>824.8050178988709</v>
+        <v>824.4457063025749</v>
       </c>
     </row>
     <row r="3">
@@ -458,13 +458,13 @@
         <v>35</v>
       </c>
       <c r="B3" t="n">
-        <v>97.72111173218141</v>
+        <v>93.72935401912012</v>
       </c>
       <c r="C3" t="n">
-        <v>375.5677106619204</v>
+        <v>372.7673591053548</v>
       </c>
       <c r="D3" t="n">
-        <v>929.5348000540448</v>
+        <v>929.4848190994923</v>
       </c>
     </row>
     <row r="4">
@@ -472,13 +472,13 @@
         <v>40</v>
       </c>
       <c r="B4" t="n">
-        <v>65.38816261402206</v>
+        <v>61.45633654502038</v>
       </c>
       <c r="C4" t="n">
-        <v>326.1432572398589</v>
+        <v>329.0550268605184</v>
       </c>
       <c r="D4" t="n">
-        <v>991.1009269114203</v>
+        <v>991.1527367733021</v>
       </c>
     </row>
     <row r="5">
@@ -486,13 +486,13 @@
         <v>45</v>
       </c>
       <c r="B5" t="n">
-        <v>34.51716087313276</v>
+        <v>38.52892040326458</v>
       </c>
       <c r="C5" t="n">
-        <v>267.4348543220206</v>
+        <v>268.5546069003628</v>
       </c>
       <c r="D5" t="n">
-        <v>994.2890635909083</v>
+        <v>992.3507457961641</v>
       </c>
     </row>
     <row r="6">
@@ -500,13 +500,13 @@
         <v>50</v>
       </c>
       <c r="B6" t="n">
-        <v>12.65013179790133</v>
+        <v>12.8627345321276</v>
       </c>
       <c r="C6" t="n">
-        <v>206.0091371617102</v>
+        <v>197.2425584504658</v>
       </c>
       <c r="D6" t="n">
-        <v>933.9850142311033</v>
+        <v>932.1137956257002</v>
       </c>
     </row>
     <row r="7">
@@ -514,13 +514,13 @@
         <v>55</v>
       </c>
       <c r="B7" t="n">
-        <v>1.653563046520059</v>
+        <v>6.175327966163941</v>
       </c>
       <c r="C7" t="n">
-        <v>130.1914409368007</v>
+        <v>132.9681906985996</v>
       </c>
       <c r="D7" t="n">
-        <v>818.5722417238519</v>
+        <v>824.5284426151333</v>
       </c>
     </row>
     <row r="8">
@@ -528,13 +528,13 @@
         <v>60</v>
       </c>
       <c r="B8" t="n">
-        <v>1.571047556079149</v>
+        <v>-0.9034801727384667</v>
       </c>
       <c r="C8" t="n">
-        <v>71.95981028174673</v>
+        <v>72.105382941838</v>
       </c>
       <c r="D8" t="n">
-        <v>666.4484822874402</v>
+        <v>677.3687641007734</v>
       </c>
     </row>
     <row r="9">
@@ -542,13 +542,13 @@
         <v>65</v>
       </c>
       <c r="B9" t="n">
-        <v>12.68962676869912</v>
+        <v>14.35758351276477</v>
       </c>
       <c r="C9" t="n">
-        <v>27.3700511004334</v>
+        <v>26.74856830780232</v>
       </c>
       <c r="D9" t="n">
-        <v>496.8935892142599</v>
+        <v>499.4892642294593</v>
       </c>
     </row>
     <row r="10">
@@ -556,13 +556,13 @@
         <v>70</v>
       </c>
       <c r="B10" t="n">
-        <v>35.17633028082958</v>
+        <v>34.65608388166847</v>
       </c>
       <c r="C10" t="n">
-        <v>-1.978345582316195</v>
+        <v>13.82701094028012</v>
       </c>
       <c r="D10" t="n">
-        <v>329.6315490428585</v>
+        <v>327.4523337086154</v>
       </c>
     </row>
     <row r="11">
@@ -570,13 +570,13 @@
         <v>75</v>
       </c>
       <c r="B11" t="n">
-        <v>67.88958038145212</v>
+        <v>64.0637779803953</v>
       </c>
       <c r="C11" t="n">
-        <v>2.138631240061756</v>
+        <v>3.499503822747249</v>
       </c>
       <c r="D11" t="n">
-        <v>179.2534735355453</v>
+        <v>175.90828860709</v>
       </c>
     </row>
     <row r="12">
@@ -584,13 +584,13 @@
         <v>80</v>
       </c>
       <c r="B12" t="n">
-        <v>96.11407178035499</v>
+        <v>97.7154851505837</v>
       </c>
       <c r="C12" t="n">
-        <v>25.30267674317626</v>
+        <v>28.88085366479165</v>
       </c>
       <c r="D12" t="n">
-        <v>63.90095457502222</v>
+        <v>69.23044778914723</v>
       </c>
     </row>
     <row r="13">
@@ -598,13 +598,13 @@
         <v>85</v>
       </c>
       <c r="B13" t="n">
-        <v>135.5200135082353</v>
+        <v>130.0167214635605</v>
       </c>
       <c r="C13" t="n">
-        <v>73.74491377629687</v>
+        <v>74.3045613599115</v>
       </c>
       <c r="D13" t="n">
-        <v>11.61249384589292</v>
+        <v>7.345988688462048</v>
       </c>
     </row>
     <row r="14">
@@ -612,13 +612,13 @@
         <v>90</v>
       </c>
       <c r="B14" t="n">
-        <v>160.064596429522</v>
+        <v>161.3367393523625</v>
       </c>
       <c r="C14" t="n">
-        <v>127.6747548041641</v>
+        <v>126.7106539165878</v>
       </c>
       <c r="D14" t="n">
-        <v>6.973260614411233</v>
+        <v>9.203090819458358</v>
       </c>
     </row>
     <row r="15">
@@ -626,13 +626,13 @@
         <v>95</v>
       </c>
       <c r="B15" t="n">
-        <v>187.3104237557953</v>
+        <v>186.4703852298835</v>
       </c>
       <c r="C15" t="n">
-        <v>198.6068293655372</v>
+        <v>195.0340179698259</v>
       </c>
       <c r="D15" t="n">
-        <v>70.35074733012576</v>
+        <v>70.02513226507736</v>
       </c>
     </row>
     <row r="16">
@@ -640,13 +640,13 @@
         <v>100</v>
       </c>
       <c r="B16" t="n">
-        <v>199.8802084100779</v>
+        <v>199.9562473873465</v>
       </c>
       <c r="C16" t="n">
-        <v>268.7238788299074</v>
+        <v>263.6913440162311</v>
       </c>
       <c r="D16" t="n">
-        <v>176.3457133697485</v>
+        <v>179.8745662361619</v>
       </c>
     </row>
   </sheetData>

--- a/monet/tests/TestData/calibrate/pwrmeasured_488nm.xlsx
+++ b/monet/tests/TestData/calibrate/pwrmeasured_488nm.xlsx
@@ -444,13 +444,13 @@
         <v>30</v>
       </c>
       <c r="B2" t="n">
-        <v>132.6974911867955</v>
+        <v>135.7043420529317</v>
       </c>
       <c r="C2" t="n">
-        <v>398.7140033108793</v>
+        <v>399.3614312609629</v>
       </c>
       <c r="D2" t="n">
-        <v>824.4457063025749</v>
+        <v>820.6592257090977</v>
       </c>
     </row>
     <row r="3">
@@ -458,13 +458,13 @@
         <v>35</v>
       </c>
       <c r="B3" t="n">
-        <v>93.72935401912012</v>
+        <v>101.2203616207431</v>
       </c>
       <c r="C3" t="n">
-        <v>372.7673591053548</v>
+        <v>375.3575064651312</v>
       </c>
       <c r="D3" t="n">
-        <v>929.4848190994923</v>
+        <v>933.5194154849069</v>
       </c>
     </row>
     <row r="4">
@@ -472,13 +472,13 @@
         <v>40</v>
       </c>
       <c r="B4" t="n">
-        <v>61.45633654502038</v>
+        <v>66.5883181337273</v>
       </c>
       <c r="C4" t="n">
-        <v>329.0550268605184</v>
+        <v>327.5360740795004</v>
       </c>
       <c r="D4" t="n">
-        <v>991.1527367733021</v>
+        <v>990.9306477192287</v>
       </c>
     </row>
     <row r="5">
@@ -486,13 +486,13 @@
         <v>45</v>
       </c>
       <c r="B5" t="n">
-        <v>38.52892040326458</v>
+        <v>32.47015149531685</v>
       </c>
       <c r="C5" t="n">
-        <v>268.5546069003628</v>
+        <v>270.243601627607</v>
       </c>
       <c r="D5" t="n">
-        <v>992.3507457961641</v>
+        <v>997.7742751857081</v>
       </c>
     </row>
     <row r="6">
@@ -500,13 +500,13 @@
         <v>50</v>
       </c>
       <c r="B6" t="n">
-        <v>12.8627345321276</v>
+        <v>13.91756217870683</v>
       </c>
       <c r="C6" t="n">
-        <v>197.2425584504658</v>
+        <v>197.6290868495559</v>
       </c>
       <c r="D6" t="n">
-        <v>932.1137956257002</v>
+        <v>927.9467889407729</v>
       </c>
     </row>
     <row r="7">
@@ -514,13 +514,13 @@
         <v>55</v>
       </c>
       <c r="B7" t="n">
-        <v>6.175327966163941</v>
+        <v>1.417112873256164</v>
       </c>
       <c r="C7" t="n">
-        <v>132.9681906985996</v>
+        <v>134.6425685623223</v>
       </c>
       <c r="D7" t="n">
-        <v>824.5284426151333</v>
+        <v>820.9980956004721</v>
       </c>
     </row>
     <row r="8">
@@ -528,13 +528,13 @@
         <v>60</v>
       </c>
       <c r="B8" t="n">
-        <v>-0.9034801727384667</v>
+        <v>0.09758438443507389</v>
       </c>
       <c r="C8" t="n">
-        <v>72.105382941838</v>
+        <v>67.59480813035486</v>
       </c>
       <c r="D8" t="n">
-        <v>677.3687641007734</v>
+        <v>673.3804117233676</v>
       </c>
     </row>
     <row r="9">
@@ -542,13 +542,13 @@
         <v>65</v>
       </c>
       <c r="B9" t="n">
-        <v>14.35758351276477</v>
+        <v>10.16924285962251</v>
       </c>
       <c r="C9" t="n">
-        <v>26.74856830780232</v>
+        <v>26.17372096368529</v>
       </c>
       <c r="D9" t="n">
-        <v>499.4892642294593</v>
+        <v>502.8234723777939</v>
       </c>
     </row>
     <row r="10">
@@ -556,13 +556,13 @@
         <v>70</v>
       </c>
       <c r="B10" t="n">
-        <v>34.65608388166847</v>
+        <v>36.54845043589131</v>
       </c>
       <c r="C10" t="n">
-        <v>13.82701094028012</v>
+        <v>10.60837587727724</v>
       </c>
       <c r="D10" t="n">
-        <v>327.4523337086154</v>
+        <v>329.2022201113473</v>
       </c>
     </row>
     <row r="11">
@@ -570,13 +570,13 @@
         <v>75</v>
       </c>
       <c r="B11" t="n">
-        <v>64.0637779803953</v>
+        <v>65.89048570872795</v>
       </c>
       <c r="C11" t="n">
-        <v>3.499503822747249</v>
+        <v>6.079105282157141</v>
       </c>
       <c r="D11" t="n">
-        <v>175.90828860709</v>
+        <v>174.0285767598176</v>
       </c>
     </row>
     <row r="12">
@@ -584,13 +584,13 @@
         <v>80</v>
       </c>
       <c r="B12" t="n">
-        <v>97.7154851505837</v>
+        <v>103.1408038748563</v>
       </c>
       <c r="C12" t="n">
-        <v>28.88085366479165</v>
+        <v>27.1054524426869</v>
       </c>
       <c r="D12" t="n">
-        <v>69.23044778914723</v>
+        <v>70.2872343596754</v>
       </c>
     </row>
     <row r="13">
@@ -598,13 +598,13 @@
         <v>85</v>
       </c>
       <c r="B13" t="n">
-        <v>130.0167214635605</v>
+        <v>129.9865916258576</v>
       </c>
       <c r="C13" t="n">
-        <v>74.3045613599115</v>
+        <v>74.2448910803007</v>
       </c>
       <c r="D13" t="n">
-        <v>7.345988688462048</v>
+        <v>10.14304093597494</v>
       </c>
     </row>
     <row r="14">
@@ -612,13 +612,13 @@
         <v>90</v>
       </c>
       <c r="B14" t="n">
-        <v>161.3367393523625</v>
+        <v>164.8453190390451</v>
       </c>
       <c r="C14" t="n">
-        <v>126.7106539165878</v>
+        <v>132.0455582200986</v>
       </c>
       <c r="D14" t="n">
-        <v>9.203090819458358</v>
+        <v>11.32985917520289</v>
       </c>
     </row>
     <row r="15">
@@ -626,13 +626,13 @@
         <v>95</v>
       </c>
       <c r="B15" t="n">
-        <v>186.4703852298835</v>
+        <v>187.6582632171649</v>
       </c>
       <c r="C15" t="n">
-        <v>195.0340179698259</v>
+        <v>201.393758633546</v>
       </c>
       <c r="D15" t="n">
-        <v>70.02513226507736</v>
+        <v>71.76551219165664</v>
       </c>
     </row>
     <row r="16">
@@ -640,13 +640,13 @@
         <v>100</v>
       </c>
       <c r="B16" t="n">
-        <v>199.9562473873465</v>
+        <v>201.2749069506121</v>
       </c>
       <c r="C16" t="n">
-        <v>263.6913440162311</v>
+        <v>274.5298104229275</v>
       </c>
       <c r="D16" t="n">
-        <v>179.8745662361619</v>
+        <v>180.4148011851619</v>
       </c>
     </row>
   </sheetData>

--- a/monet/tests/TestData/calibrate/pwrmeasured_488nm.xlsx
+++ b/monet/tests/TestData/calibrate/pwrmeasured_488nm.xlsx
@@ -444,13 +444,13 @@
         <v>30</v>
       </c>
       <c r="B2" t="n">
-        <v>135.7043420529317</v>
+        <v>134.8243729801019</v>
       </c>
       <c r="C2" t="n">
-        <v>399.3614312609629</v>
+        <v>398.1323105225044</v>
       </c>
       <c r="D2" t="n">
-        <v>820.6592257090977</v>
+        <v>819.6906126376971</v>
       </c>
     </row>
     <row r="3">
@@ -458,13 +458,13 @@
         <v>35</v>
       </c>
       <c r="B3" t="n">
-        <v>101.2203616207431</v>
+        <v>99.51541745916255</v>
       </c>
       <c r="C3" t="n">
-        <v>375.3575064651312</v>
+        <v>373.6425920477699</v>
       </c>
       <c r="D3" t="n">
-        <v>933.5194154849069</v>
+        <v>932.4382187386404</v>
       </c>
     </row>
     <row r="4">
@@ -472,13 +472,13 @@
         <v>40</v>
       </c>
       <c r="B4" t="n">
-        <v>66.5883181337273</v>
+        <v>68.84522069991581</v>
       </c>
       <c r="C4" t="n">
-        <v>327.5360740795004</v>
+        <v>327.8797741965989</v>
       </c>
       <c r="D4" t="n">
-        <v>990.9306477192287</v>
+        <v>995.9575585357959</v>
       </c>
     </row>
     <row r="5">
@@ -486,13 +486,13 @@
         <v>45</v>
       </c>
       <c r="B5" t="n">
-        <v>32.47015149531685</v>
+        <v>33.59080247183161</v>
       </c>
       <c r="C5" t="n">
-        <v>270.243601627607</v>
+        <v>266.1075901471268</v>
       </c>
       <c r="D5" t="n">
-        <v>997.7742751857081</v>
+        <v>993.1196199942332</v>
       </c>
     </row>
     <row r="6">
@@ -500,13 +500,13 @@
         <v>50</v>
       </c>
       <c r="B6" t="n">
-        <v>13.91756217870683</v>
+        <v>18.884685112048</v>
       </c>
       <c r="C6" t="n">
-        <v>197.6290868495559</v>
+        <v>203.4765509264967</v>
       </c>
       <c r="D6" t="n">
-        <v>927.9467889407729</v>
+        <v>937.1188311471718</v>
       </c>
     </row>
     <row r="7">
@@ -514,13 +514,13 @@
         <v>55</v>
       </c>
       <c r="B7" t="n">
-        <v>1.417112873256164</v>
+        <v>3.09698841872015</v>
       </c>
       <c r="C7" t="n">
-        <v>134.6425685623223</v>
+        <v>134.7002010922058</v>
       </c>
       <c r="D7" t="n">
-        <v>820.9980956004721</v>
+        <v>818.7975936301411</v>
       </c>
     </row>
     <row r="8">
@@ -528,13 +528,13 @@
         <v>60</v>
       </c>
       <c r="B8" t="n">
-        <v>0.09758438443507389</v>
+        <v>-1.665727011209204</v>
       </c>
       <c r="C8" t="n">
-        <v>67.59480813035486</v>
+        <v>70.88371744436017</v>
       </c>
       <c r="D8" t="n">
-        <v>673.3804117233676</v>
+        <v>675.1587626832247</v>
       </c>
     </row>
     <row r="9">
@@ -542,13 +542,13 @@
         <v>65</v>
       </c>
       <c r="B9" t="n">
-        <v>10.16924285962251</v>
+        <v>14.18361202611889</v>
       </c>
       <c r="C9" t="n">
-        <v>26.17372096368529</v>
+        <v>31.45786020310274</v>
       </c>
       <c r="D9" t="n">
-        <v>502.8234723777939</v>
+        <v>501.148104015168</v>
       </c>
     </row>
     <row r="10">
@@ -556,13 +556,13 @@
         <v>70</v>
       </c>
       <c r="B10" t="n">
-        <v>36.54845043589131</v>
+        <v>34.31763751795209</v>
       </c>
       <c r="C10" t="n">
-        <v>10.60837587727724</v>
+        <v>2.242272214264147</v>
       </c>
       <c r="D10" t="n">
-        <v>329.2022201113473</v>
+        <v>327.047234066685</v>
       </c>
     </row>
     <row r="11">
@@ -570,13 +570,13 @@
         <v>75</v>
       </c>
       <c r="B11" t="n">
-        <v>65.89048570872795</v>
+        <v>67.27002176430832</v>
       </c>
       <c r="C11" t="n">
-        <v>6.079105282157141</v>
+        <v>4.604350199955332</v>
       </c>
       <c r="D11" t="n">
-        <v>174.0285767598176</v>
+        <v>176.2199526707305</v>
       </c>
     </row>
     <row r="12">
@@ -584,13 +584,13 @@
         <v>80</v>
       </c>
       <c r="B12" t="n">
-        <v>103.1408038748563</v>
+        <v>100.6515716557555</v>
       </c>
       <c r="C12" t="n">
-        <v>27.1054524426869</v>
+        <v>24.60395734557181</v>
       </c>
       <c r="D12" t="n">
-        <v>70.2872343596754</v>
+        <v>62.93058088831274</v>
       </c>
     </row>
     <row r="13">
@@ -598,13 +598,13 @@
         <v>85</v>
       </c>
       <c r="B13" t="n">
-        <v>129.9865916258576</v>
+        <v>135.322186497662</v>
       </c>
       <c r="C13" t="n">
-        <v>74.2448910803007</v>
+        <v>73.59042072128517</v>
       </c>
       <c r="D13" t="n">
-        <v>10.14304093597494</v>
+        <v>5.460314953062937</v>
       </c>
     </row>
     <row r="14">
@@ -612,13 +612,13 @@
         <v>90</v>
       </c>
       <c r="B14" t="n">
-        <v>164.8453190390451</v>
+        <v>167.3219185681453</v>
       </c>
       <c r="C14" t="n">
-        <v>132.0455582200986</v>
+        <v>132.1497460102285</v>
       </c>
       <c r="D14" t="n">
-        <v>11.32985917520289</v>
+        <v>8.276174195524003</v>
       </c>
     </row>
     <row r="15">
@@ -626,13 +626,13 @@
         <v>95</v>
       </c>
       <c r="B15" t="n">
-        <v>187.6582632171649</v>
+        <v>185.1497170398162</v>
       </c>
       <c r="C15" t="n">
-        <v>201.393758633546</v>
+        <v>198.0178493666491</v>
       </c>
       <c r="D15" t="n">
-        <v>71.76551219165664</v>
+        <v>69.36912759839244</v>
       </c>
     </row>
     <row r="16">
@@ -640,13 +640,13 @@
         <v>100</v>
       </c>
       <c r="B16" t="n">
-        <v>201.2749069506121</v>
+        <v>197.6662798826911</v>
       </c>
       <c r="C16" t="n">
-        <v>274.5298104229275</v>
+        <v>267.2158562603944</v>
       </c>
       <c r="D16" t="n">
-        <v>180.4148011851619</v>
+        <v>182.326720803949</v>
       </c>
     </row>
   </sheetData>
